--- a/artfynd/A 36463-2023 artfynd.xlsx
+++ b/artfynd/A 36463-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36463-2023 artfynd.xlsx
+++ b/artfynd/A 36463-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80923863</v>
+        <v>1927297</v>
       </c>
       <c r="B2" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hasslörondellen, Ö om, Bl</t>
+          <t>SO om Hasslörondellen, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529674.1092433297</v>
+        <v>529554</v>
       </c>
       <c r="R2" t="n">
-        <v>6228137.254477757</v>
+        <v>6228067</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-12-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-12-11</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd (ÅGP)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,22 +759,465 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1927301</v>
+      </c>
+      <c r="B3" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>SO om Hasslörondellen, Bl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>529571</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6228087</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Förkärla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2009-12-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2009-12-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd (ÅGP)</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1927303</v>
+      </c>
+      <c r="B4" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SO om Hasslörondellen, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>529572</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6228101</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Förkärla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-12-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-12-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd (ÅGP)</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1928493</v>
+      </c>
+      <c r="B5" t="n">
+        <v>75300</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SO om Hasslörondellen, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>529584</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6228137</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Förkärla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2009-12-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2009-12-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Inventering av skyddsvärda träd (ÅGP)</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mattias Lif</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för hotade arter</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>80923863</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111176</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hasslörondellen, Ö om, Bl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>529674</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6228137</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ronneby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Förkärla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2019-06-27</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2019-06-27</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Tore Mattsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Tore Mattsson, Olle Molander</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
